--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,23 +500,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>clang-tidy failed, coverage failed</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -860,7 +856,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>clang-tidy not installed</t>
+          <t>no compile_commands.json — clang-tidy skipped (run cmake with CMAKE_EXPORT_COMPILE_COMMANDS=ON)</t>
         </is>
       </c>
     </row>
@@ -877,12 +873,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>74 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>All C/C++ files excluded by exclude_paths</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1525,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Line coverage 0.0% &lt; 40.0%</t>
+          <t>coverage.enabled=false — C coverage via c-coverage-gate</t>
         </is>
       </c>
     </row>
